--- a/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D36_r1_Missing-rate-and-procurement-report.xlsx
+++ b/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D36_r1_Missing-rate-and-procurement-report.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unpriced schedule lines (nev" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unpriced or incomplete BOQ l" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement needs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resolved exceptions from the" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions recorded in the f" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,12 +620,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,27 +638,1320 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Excavation in pits for footings</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>314.04 m3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PCC blinding 50 mm under footings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>18.33 m3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Backfill around footings</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>240.58 m3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Isolated footings</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>55.4 m3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Columns — Foundation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.9 m3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Columns — Ground floor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.3 m3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Columns — First floor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.56 m3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>First-floor beams 200x450</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5.21 m3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Roof beams 200x300</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2.15 m3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Slab — Ground floor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>22.14 m3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Slab — First floor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>22.35 m3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Slab — Roof</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11.29 m3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RC stairs (flights + landings)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.13 m3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Footing sides</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>249.59 m2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Column faces</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>119.38 m2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Beam sides and soffit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>493.69 m2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Slab soffit and edges</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>884.02 m2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Walls — Ground floor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>58.94 m3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Walls — First floor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>43.41 m3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Walls — Roof</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9.04 m3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wall plaster area, both faces (gross)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1345.2 m2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Door 900 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7 nr</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Door 800 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4 nr</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Door 802 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Door 6467 × 3140 mm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Door 2400 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Door 736 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Door 1300 × 2400 mm</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Window 800 × 400 mm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3 nr</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Window 2460 × 600 mm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Window 3000 × 600 mm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Window 2600 × 600 mm</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Window 387 × 3140 mm</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Window 368 × 3140 mm</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Window 1500 × 400 mm</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Window 600 × 2950 mm</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5.16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Window 1206 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Window 1800 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Window 2400 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Window 1160 × 2750 mm</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Window 1200 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2 nr</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Window 4274 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Window 2500 × 1600 mm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5.23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Window 4000 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Window 2400 × 2100 mm</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Window 2400 × 1600 mm</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1 nr</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Railings and balustrades</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>43.68 m</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Roof and canopy members</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>48.85 m</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>unpriced</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
